--- a/问题三/results/表2_指定日期充放电量.xlsx
+++ b/问题三/results/表2_指定日期充放电量.xlsx
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5333.333333333332</v>
+        <v>5333.333333333333</v>
       </c>
       <c r="D25" t="n">
         <v>2842.525766666667</v>

--- a/问题三/results/表2_指定日期充放电量.xlsx
+++ b/问题三/results/表2_指定日期充放电量.xlsx
@@ -474,10 +474,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4499.999999999999</v>
+        <v>145.6720458333332</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>548.2837916666672</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6000</v>
+        <v>10384.4345969787</v>
       </c>
     </row>
     <row r="3">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>833.3333333333333</v>
+        <v>766.8914226985619</v>
       </c>
       <c r="D3" t="n">
-        <v>7426.613433333336</v>
+        <v>5555.926913624999</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6000.000000000004</v>
+        <v>10122.11633370371</v>
       </c>
     </row>
     <row r="4">
@@ -516,10 +516,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1858.083060493823</v>
+        <v>5263.320197427985</v>
       </c>
       <c r="D4" t="n">
-        <v>1213.386566666666</v>
+        <v>2777.377216666667</v>
       </c>
     </row>
     <row r="5">
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9734.769083333333</v>
+        <v>5565.251603189296</v>
       </c>
       <c r="D5" t="n">
-        <v>868.5431365000006</v>
+        <v>254.722783333333</v>
       </c>
     </row>
     <row r="6">
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>146.0900000000001</v>
+        <v>37.32360596707723</v>
       </c>
       <c r="D6" t="n">
-        <v>5709.783516666664</v>
+        <v>5579.067624666665</v>
       </c>
     </row>
     <row r="7">
@@ -555,10 +555,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5333.333333333332</v>
+        <v>9818.510416666666</v>
       </c>
       <c r="D7" t="n">
-        <v>2930.216483333334</v>
+        <v>3014.253233333334</v>
       </c>
     </row>
     <row r="8">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>707.8857333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>761.4409166666663</v>
+        <v>3215.096578291675</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6000</v>
+        <v>9810.413472916674</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>533.5582749999998</v>
       </c>
       <c r="D9" t="n">
-        <v>3558.559083333334</v>
+        <v>4836.610433333333</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6000</v>
+        <v>10345.4071237963</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2716.291333333336</v>
+        <v>9798.47560401235</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7918.88783333333</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>31.48750000000018</v>
+        <v>95.1419170781884</v>
       </c>
       <c r="D12" t="n">
-        <v>6154.100616666667</v>
+        <v>4276.431303666666</v>
       </c>
     </row>
     <row r="13">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5333.333333333333</v>
+        <v>7748.307834053497</v>
       </c>
       <c r="D13" t="n">
-        <v>2485.899383333333</v>
+        <v>2485.896583333333</v>
       </c>
     </row>
     <row r="14">
@@ -672,10 +672,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4499.999999999999</v>
+        <v>3152.220011698549</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>173.1673500000003</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6000</v>
+        <v>6691.287730675004</v>
       </c>
     </row>
     <row r="15">
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>833.3333333333333</v>
+        <v>962.0169666666668</v>
       </c>
       <c r="D15" t="n">
-        <v>6399.833181999998</v>
+        <v>5015.371791666666</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6000.000000000004</v>
+        <v>6755.347979075785</v>
       </c>
     </row>
     <row r="16">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3907.725033333333</v>
+        <v>3946.256118057458</v>
       </c>
       <c r="D16" t="n">
-        <v>780.0466166666658</v>
+        <v>1896.615716666666</v>
       </c>
     </row>
     <row r="17">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6415.392024485602</v>
+        <v>5750.149888012499</v>
       </c>
       <c r="D17" t="n">
-        <v>1202.573066666667</v>
+        <v>403.6249166666665</v>
       </c>
     </row>
     <row r="18">
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25.59018333333347</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5602.909066666667</v>
+        <v>5591.766322956793</v>
       </c>
     </row>
     <row r="19">
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5333.333333333333</v>
+        <v>5758.650771553497</v>
       </c>
       <c r="D19" t="n">
-        <v>3037.090933333336</v>
+        <v>2712.927620833333</v>
       </c>
     </row>
     <row r="20">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4499.999999999999</v>
+        <v>842.2689958333335</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1615.635295003047</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>6000</v>
+        <v>10236.43656772977</v>
       </c>
     </row>
     <row r="21">
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1665.683983333333</v>
+        <v>2453.806099744702</v>
       </c>
       <c r="D21" t="n">
-        <v>1775.416697999996</v>
+        <v>2120.34276249123</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6000.000000000002</v>
+        <v>10218.73872449074</v>
       </c>
     </row>
     <row r="22">
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5833.333333333333</v>
+        <v>3618.647312996046</v>
       </c>
       <c r="D22" t="n">
-        <v>7143.381566666669</v>
+        <v>4698.371565717103</v>
       </c>
     </row>
     <row r="23">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8312.889409259256</v>
+        <v>6546.630657322883</v>
       </c>
       <c r="D23" t="n">
-        <v>3213.846183333333</v>
+        <v>2849.048012499999</v>
       </c>
     </row>
     <row r="24">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>322.8449489066477</v>
       </c>
       <c r="D24" t="n">
-        <v>5797.474233333332</v>
+        <v>5277.96223763039</v>
       </c>
     </row>
     <row r="25">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5333.333333333333</v>
+        <v>9955.868933333335</v>
       </c>
       <c r="D25" t="n">
-        <v>2842.525766666667</v>
+        <v>2684.022413564279</v>
       </c>
     </row>
   </sheetData>

--- a/问题三/results/表2_指定日期充放电量.xlsx
+++ b/问题三/results/表2_指定日期充放电量.xlsx
@@ -474,10 +474,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>145.6720458333332</v>
+        <v>1351.428258745291</v>
       </c>
       <c r="D2" t="n">
-        <v>548.2837916666672</v>
+        <v>280.1505458333336</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10384.4345969787</v>
+        <v>8716.041200582022</v>
       </c>
     </row>
     <row r="3">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>766.8914226985619</v>
+        <v>941.9890458333334</v>
       </c>
       <c r="D3" t="n">
-        <v>5555.926913624999</v>
+        <v>5972.472716232509</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10122.11633370371</v>
+        <v>6576.767124577153</v>
       </c>
     </row>
     <row r="4">
@@ -516,10 +516,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5263.320197427985</v>
+        <v>5200.2239</v>
       </c>
       <c r="D4" t="n">
-        <v>2777.377216666667</v>
+        <v>2369.481835166663</v>
       </c>
     </row>
     <row r="5">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5565.251603189296</v>
+        <v>5780.915338683129</v>
       </c>
       <c r="D5" t="n">
         <v>254.722783333333</v>
@@ -542,10 +542,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37.32360596707723</v>
+        <v>33.23153806584337</v>
       </c>
       <c r="D6" t="n">
-        <v>5579.067624666665</v>
+        <v>5671.120099060698</v>
       </c>
     </row>
     <row r="7">
@@ -555,10 +555,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9818.510416666666</v>
+        <v>6044.723182526916</v>
       </c>
       <c r="D7" t="n">
-        <v>3014.253233333334</v>
+        <v>3052.932812500001</v>
       </c>
     </row>
     <row r="8">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>707.8857333333333</v>
+        <v>975.5033083333337</v>
       </c>
       <c r="D8" t="n">
-        <v>3215.096578291675</v>
+        <v>502.1065607499999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9810.413472916674</v>
+        <v>4565.58393762566</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>533.5582749999998</v>
+        <v>579.0785000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>4836.610433333333</v>
+        <v>3091.432185529761</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10345.4071237963</v>
+        <v>4821.601621388888</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9798.47560401235</v>
+        <v>9809.014737860083</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>95.1419170781884</v>
+        <v>298.9055416666664</v>
       </c>
       <c r="D12" t="n">
-        <v>4276.431303666666</v>
+        <v>5157.720566666666</v>
       </c>
     </row>
     <row r="13">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7748.307834053497</v>
+        <v>2494.993975925924</v>
       </c>
       <c r="D13" t="n">
         <v>2485.896583333333</v>
@@ -672,10 +672,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3152.220011698549</v>
+        <v>1731.085596328815</v>
       </c>
       <c r="D14" t="n">
-        <v>173.1673500000003</v>
+        <v>276.7784791666669</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6691.287730675004</v>
+        <v>8086.08610418369</v>
       </c>
     </row>
     <row r="15">
@@ -696,7 +696,7 @@
         <v>962.0169666666668</v>
       </c>
       <c r="D15" t="n">
-        <v>5015.371791666666</v>
+        <v>5059.058141666666</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6755.347979075785</v>
+        <v>7549.646062422704</v>
       </c>
     </row>
     <row r="16">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3946.256118057458</v>
+        <v>2956.173516666666</v>
       </c>
       <c r="D16" t="n">
         <v>1896.615716666666</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5750.149888012499</v>
+        <v>6793.439673919758</v>
       </c>
       <c r="D17" t="n">
         <v>403.6249166666665</v>
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>73.32112463801592</v>
       </c>
       <c r="D18" t="n">
-        <v>5591.766322956793</v>
+        <v>5685.278787821434</v>
       </c>
     </row>
     <row r="19">
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5758.650771553497</v>
+        <v>6729.512174901329</v>
       </c>
       <c r="D19" t="n">
-        <v>2712.927620833333</v>
+        <v>2750.334728625002</v>
       </c>
     </row>
     <row r="20">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>842.2689958333335</v>
+        <v>2640.205295659843</v>
       </c>
       <c r="D20" t="n">
-        <v>1615.635295003047</v>
+        <v>69.47882500000003</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10236.43656772977</v>
+        <v>6694.911306089167</v>
       </c>
     </row>
     <row r="21">
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2453.806099744702</v>
+        <v>2602.016541666667</v>
       </c>
       <c r="D21" t="n">
-        <v>2120.34276249123</v>
+        <v>2100.002470291667</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10218.73872449074</v>
+        <v>7387.324682457252</v>
       </c>
     </row>
     <row r="22">
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3618.647312996046</v>
+        <v>4231.857081525035</v>
       </c>
       <c r="D22" t="n">
-        <v>4698.371565717103</v>
+        <v>4717.822857916665</v>
       </c>
     </row>
     <row r="23">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6546.630657322883</v>
+        <v>6770.293250154316</v>
       </c>
       <c r="D23" t="n">
-        <v>2849.048012499999</v>
+        <v>2576.057479166666</v>
       </c>
     </row>
     <row r="24">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>322.8449489066477</v>
+        <v>46.62864711934258</v>
       </c>
       <c r="D24" t="n">
-        <v>5277.96223763039</v>
+        <v>5639.967917510246</v>
       </c>
     </row>
     <row r="25">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9955.868933333335</v>
+        <v>6696.917781498077</v>
       </c>
       <c r="D25" t="n">
-        <v>2684.022413564279</v>
+        <v>2893.712475458333</v>
       </c>
     </row>
   </sheetData>
